--- a/windfarm-radar/docs/CAP670-verification-checklist.xlsx
+++ b/windfarm-radar/docs/CAP670-verification-checklist.xlsx
@@ -2778,7 +2778,7 @@
       <c r="A92"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOTAL: 80 checks. 70 confirmed, 7 corrected, 3 still open.</t>
+          <t xml:space="preserve">J. WHAT SUR 13 SAYS ABOUT THE MITIGATIONS THIS TOOL OFFERS</t>
         </is>
       </c>
       <c r="C92"/>
@@ -2787,6 +2787,343 @@
       <c r="F92"/>
       <c r="G92"/>
     </row>
+    <row r="93">
+      <c r="A93">
+        <v>81</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sector blanking</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the tool sizes the coverage hole and now states the condition</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"PSR sector blanking for the purposes of mitigating wind turbine effects on a controller’s display shall only be permitted where the ANSP provides a robust safety argument that total loss of all surveillance data on the blanked areas would cause no safety related impact."</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmed</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAP 670 SUR 13.40 and SUR 13.41</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added in the second pass. The tool did not previously carry this condition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>82</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference target size for a threshold assessment</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 dBsm (1 m2)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The threshold set shall take in to account the RCS of the largest wind turbine in the area affected, the largest fixed clutter (other than turbine), and a 1m2 target likely to fly within the area of interest."</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmed</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAP 670 SUR 13.43 and SUR 13.44</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The only numeric target size CAP 670 names anywhere in its wind turbine material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>83</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Are these mitigations CAA-endorsed?</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no, and the tool does not say they are</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"ANSPs are also reminded that the mitigation mechanisms listed here are guidance only and must not be regarded as mitigations that are recommended or endorsed by the CAA."</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmed</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAP 670 SUR 13A.107</t>
+        </is>
+      </c>
+      <c r="G95"/>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>84</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10 km SSR proximity figure</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10 km</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"These effects are only a consideration when the turbines are located very close to the SSR, i.e less than 10 km."</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmed</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAP 670 SUR 13A.75</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Was carried on a CAP 764 search summary alone. Now corroborated by a document that was read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. FIGURES CAP 670 CANNOT ADJUDICATE, AND WHY</t>
+        </is>
+      </c>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>85</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 30 km primary radar assessment guide</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used in the cap764-30km finding</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nothing applicable</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STILL OPEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">searched the whole document</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The string "30 km" does not appear anywhere in CAP 670. The figure is CAP 764’s and CAP 764 has still only been seen as a search summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>86</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radar absorbent material, 10 dB default reduction</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used in the ram mitigation</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nothing applicable</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STILL OPEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">searched the whole document</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUR 13A.105 describes RAM qualitatively, as ferrite paints or polymer layers incorporating crystalline graphite, and gives NO figure for the reduction achieved. The 10 dB default is this tool’s, not the regulator’s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>87</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhanced Doppler processing, 15 dB default extra rejection</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used in the enhancedDoppler mitigation</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nothing applicable</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STILL OPEN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">searched the whole document</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAP 670 sets conditions on amplitude, CFAR and clutter map processing but publishes no rejection figure for any of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>88</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turbine curtailment</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used in the curtail mitigation</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nothing applicable</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STILL OPEN</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">searched the whole document</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curtailment is not mentioned in CAP 670 at all. It is in the tool as a theoretical best case, not as a recognised mitigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>89</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turbine RCS defaults at microwave frequencies</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used in TURBINE_PRESETS in js/model.js</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nothing applicable</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STILL OPEN</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">searched the whole document</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAP 670 Tables 4 and 5 are calculated at 127 MHz and 368 MHz. This tool models L, S, C and X band, between 1.25 and 9.4 GHz. The published scaling formula is linear in frequency and would extrapolate, but a factor of seven beyond the highest frequency the document states is outside what it supports, and turbine RCS does not scale that simply once the wavelength is short against the blade chord. Nothing is extrapolated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL: 89 checks. 74 confirmed, 7 corrected, 8 still open.</t>
+        </is>
+      </c>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>